--- a/Digital_Village_Api/Data/citizens.xlsx
+++ b/Digital_Village_Api/Data/citizens.xlsx
@@ -69,6 +69,111 @@
   </x:si>
   <x:si>
     <x:t>DLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>mv emc s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>j jmew fme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>male</x:t>
+  </x:si>
+  <x:si>
+    <x:t>890890890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>m vvmefe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dlp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mcsmcs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">csm </x:t>
+  </x:si>
+  <x:si>
+    <x:t>8900890900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>see</x:t>
+  </x:si>
+  <x:si>
+    <x:t>yui</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vinay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8908998098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hhdh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ueheu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vijay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8908908900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vjy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Siddu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vishnu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7897898909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kkk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vishnu@123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pullaiah</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manjula</x:t>
+  </x:si>
+  <x:si>
+    <x:t>other</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8989898989</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kdp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdfghjkl;'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Password</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConfirmPassword</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -422,7 +527,7 @@
     <x:col min="7" max="7" width="18.632812" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <x:row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -447,8 +552,14 @@
       <x:c r="H1" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <x:c r="I1" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -474,7 +585,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:8">
+    <x:row r="3" spans="1:10">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -498,6 +609,420 @@
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:10">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:10">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:10">
+      <x:c r="A6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:10">
+      <x:c r="A7" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:10">
+      <x:c r="A8" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:10">
+      <x:c r="A9" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:10">
+      <x:c r="A10" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D10" s="0">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:10">
+      <x:c r="A11" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D11" s="0">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:10">
+      <x:c r="A12" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D12" s="0">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10">
+      <x:c r="A13" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D13" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="0">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="0">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D16" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="0">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D17" s="0">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
+      <x:c r="A18" s="0">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
